--- a/out/LSTM-S4_repeat_2_000006.xlsx
+++ b/out/LSTM-S4_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.462243845257878</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.986393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002591428872001124</v>
+        <v>-4.507084498507902e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3335370820859658</v>
+        <v>0.05800968834576496</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6677053767718915</v>
+        <v>0.1161291589261605</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07702742170514028</v>
+        <v>-0.01339682142461548</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2562505174936254</v>
+        <v>0.04456779607616435</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2562505174936254</v>
+        <v>0.04456779607616435</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2559781179030882</v>
+        <v>0.04450546296924632</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8368702915355349</v>
+        <v>0.1915006229217953</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.931385430509069</v>
+        <v>0.4278883564966221</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.160125762817474</v>
+        <v>0.03664154853013495</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.41354509118448</v>
+        <v>0.3093910479413942</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2804752420595613</v>
+        <v>0.06418114726498904</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.814448740383135</v>
+        <v>0.4011297553465467</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1535984492129518</v>
+        <v>0.03514793183248933</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.84092868555054</v>
+        <v>0.4071891514755304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06343859323464605</v>
+        <v>0.01451641090490868</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.814045926728836</v>
+        <v>0.4010375894616647</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07903904323709182</v>
+        <v>0.01808669269314835</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.90869606785221</v>
+        <v>0.4226966069010133</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04759112309649866</v>
+        <v>0.01088908999745086</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.924786817130075</v>
+        <v>0.4263772558927387</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03618294540989134</v>
+        <v>0.008277360874876552</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386393030374176</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.949540066894573</v>
+        <v>0.4320391647212901</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01600381091800799</v>
+        <v>0.003658318211120672</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.94533283063475</v>
+        <v>0.4310725982163479</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01269685869154589</v>
+        <v>0.002900588008868321</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.95472052186961</v>
+        <v>0.4332169246889919</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006293727303002108</v>
+        <v>0.001435852631663707</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.954603084463522</v>
+        <v>0.4331861882890922</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003657683738747592</v>
+        <v>0.0008328498147413078</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.955621806008192</v>
+        <v>0.4334156824726502</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001827796469746611</v>
+        <v>0.0004139249073706539</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.955614524052863</v>
+        <v>0.4334101608828609</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009005141711502362</v>
+        <v>0.0002019746676914826</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.955586601871184</v>
+        <v>0.4333998869329526</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005190114861307296</v>
+        <v>0.0001151555000044985</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.95572697405599</v>
+        <v>0.4334285779490068</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001713256390037807</v>
+        <v>3.517546205149434e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.955546844434433</v>
+        <v>0.4333825679861824</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>1.521212032543939e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.955542827428841</v>
+        <v>0.4333778054753831</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.955545791941586</v>
+        <v>0.4333747966035693</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.955539240055857</v>
+        <v>0.4333694101194118</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.955539618624102</v>
+        <v>0.4333660255009609</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.955532951660231</v>
+        <v>0.4333603580706872</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.955529089585135</v>
+        <v>0.4333607386057449</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.95552454227295</v>
+        <v>0.4333609669267796</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.9555246322176</v>
+        <v>0.4333610568714296</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.955523774284015</v>
+        <v>0.4333601989378447</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.95552400260505</v>
+        <v>0.4333604272588794</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.955523206940838</v>
+        <v>0.4333596315946677</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.955523269210211</v>
+        <v>0.4333596938640408</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.955523296885488</v>
+        <v>0.4333597215393176</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.955523449099511</v>
+        <v>0.4333598737533409</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.955523103158549</v>
+        <v>0.4333595278123792</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.955523179265561</v>
+        <v>0.4333596039193908</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.955523345317223</v>
+        <v>0.4333597699710524</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.955523705095823</v>
+        <v>0.4333601297496525</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.95552372585228</v>
+        <v>0.4333601505061102</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.955523829634569</v>
+        <v>0.4333602542883986</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.955524057955604</v>
+        <v>0.4333604826094333</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.955523933416857</v>
+        <v>0.4333603580706872</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.955523961092134</v>
+        <v>0.433360385745964</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.955524016442688</v>
+        <v>0.4333604410965179</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.955524279357819</v>
+        <v>0.4333607040116487</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.955524196331988</v>
+        <v>0.4333606209858178</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.955523988767411</v>
+        <v>0.4333604134212411</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.95552400260505</v>
+        <v>0.4333604272588794</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.955524140981434</v>
+        <v>0.4333605656352641</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.955523857309846</v>
+        <v>0.4333602819636755</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.955523684339365</v>
+        <v>0.4333601089931948</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.955523580557077</v>
+        <v>0.4333600052109063</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.95552372585228</v>
+        <v>0.4333601505061102</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.955523968010954</v>
+        <v>0.4333603926647834</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.955523795040473</v>
+        <v>0.4333602196943024</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.955523497531246</v>
+        <v>0.4333599221850755</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.955523483693607</v>
+        <v>0.4333599083474369</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.955523116996188</v>
+        <v>0.4333595416500177</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.955523116996188</v>
+        <v>0.4333595416500177</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.955523054726815</v>
+        <v>0.4333594793806446</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.955522950944526</v>
+        <v>0.4333593755983561</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.955522777974045</v>
+        <v>0.4333592026278754</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.95552282640578</v>
+        <v>0.4333592510596099</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.95552246662718</v>
+        <v>0.4333588912810099</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.955522425114265</v>
+        <v>0.4333588497680945</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.955522480464818</v>
+        <v>0.4333589051186482</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.955522535815372</v>
+        <v>0.4333589604692021</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.955522577328288</v>
+        <v>0.4333590019821175</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.955522307494338</v>
+        <v>0.4333587321481674</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.955522362844891</v>
+        <v>0.4333587874987214</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.955522508140096</v>
+        <v>0.4333589327939253</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.955522473545999</v>
+        <v>0.433358898199829</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.955522459708361</v>
+        <v>0.4333588843621905</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.955522549653011</v>
+        <v>0.4333589743068407</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.955522867918695</v>
+        <v>0.4333592925725253</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.955522688029395</v>
+        <v>0.4333591126832252</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.955522729542311</v>
+        <v>0.4333591541961406</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.955522542734192</v>
+        <v>0.4333589673880213</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.955522611922384</v>
+        <v>0.4333590365762138</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.955522411276626</v>
+        <v>0.4333588359304559</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.955522452789542</v>
+        <v>0.4333588774433713</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.955522480464818</v>
+        <v>0.4333589051186482</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_2_000006.xlsx
+++ b/out/LSTM-S4_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.986393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.386393030374176</v>
+        <v>1.316383792256578</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002591428872001124</v>
+        <v>-0.0002281487710230285</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3335370820859658</v>
+        <v>0.2936452402407034</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6677053767718915</v>
+        <v>0.5878461985275054</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07702742170514028</v>
+        <v>-0.06781475573950765</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2562505174936254</v>
+        <v>0.2256023357301727</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2562505174936254</v>
+        <v>0.2256023357301727</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2559781179030882</v>
+        <v>0.2253644696726897</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8368702915355349</v>
+        <v>0.7307758094499195</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.931385430509069</v>
+        <v>1.688371559196363</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.160125762817474</v>
+        <v>0.1398257170095278</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.41354509118448</v>
+        <v>1.236180558841165</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2804752420595613</v>
+        <v>0.2449180041460473</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.814448740383135</v>
+        <v>1.58625970296179</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1535984492129518</v>
+        <v>0.1341262500444299</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.84092868555054</v>
+        <v>1.609382658935064</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06343859323464605</v>
+        <v>0.05539609458747302</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.814045926728836</v>
+        <v>1.585907991945664</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07903904323709182</v>
+        <v>0.06901878008344739</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.90869606785221</v>
+        <v>1.668558755511534</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04759112309649866</v>
+        <v>0.04155763033690184</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.386393030374176</v>
+        <v>1.116383792256578</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.924786817130075</v>
+        <v>1.682609582166163</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03618294540989134</v>
+        <v>0.03159586893928365</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386393030374176</v>
+        <v>0.4652667921121084</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.949540066894573</v>
+        <v>1.704224749934308</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01600381091800799</v>
+        <v>0.01397441300868435</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.1858502080323611</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.94533283063475</v>
+        <v>1.700550362091587</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01269685869154589</v>
+        <v>0.01108768755469</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.95472052186961</v>
+        <v>1.708747297782685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006293727303002108</v>
+        <v>0.005495755099007798</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.954603084463522</v>
+        <v>1.708644122956419</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003657683738747592</v>
+        <v>0.003192211619446865</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.955621806008192</v>
+        <v>1.709532796738187</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001827796469746611</v>
+        <v>0.001595060410096247</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.955614524052863</v>
+        <v>1.709525804554964</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009005141711502362</v>
+        <v>0.0007855282446549681</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.955586601871184</v>
+        <v>1.709500793126515</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005190114861307296</v>
+        <v>0.0004522584305726749</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.95572697405599</v>
+        <v>1.709622705614005</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001713256390037807</v>
+        <v>0.0001490059378640617</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.955546844434433</v>
+        <v>1.709464744298975</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>7.135689900721546e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.955542827428841</v>
+        <v>1.709460603042515</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.392392260217012e-05</v>
+        <v>3.658533421184461e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.955545791941586</v>
+        <v>1.709462573524107</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.955539240055857</v>
+        <v>1.70945617682695</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.955539618624102</v>
+        <v>1.709456019349447</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.955532951660231</v>
+        <v>1.709449352385576</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.955529089585135</v>
+        <v>1.70944549031048</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.95552454227295</v>
+        <v>1.709440942998295</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.9555246322176</v>
+        <v>1.709441032942945</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.955523774284015</v>
+        <v>1.70944017500936</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.95552400260505</v>
+        <v>1.709440403330394</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.955523206940838</v>
+        <v>1.709439607666183</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.955523269210211</v>
+        <v>1.709439669935556</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.955523296885488</v>
+        <v>1.709439697610833</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.955523449099511</v>
+        <v>1.709439849824856</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.955523103158549</v>
+        <v>1.709439503883894</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.955523179265561</v>
+        <v>1.709439579990906</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.955523345317223</v>
+        <v>1.709439746042567</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.955523705095823</v>
+        <v>1.709440105821167</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.95552372585228</v>
+        <v>1.709440126577625</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.955523829634569</v>
+        <v>1.709440230359913</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.955524057955604</v>
+        <v>1.709440458680948</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.955523933416857</v>
+        <v>1.709440334142202</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.955523961092134</v>
+        <v>1.709440361817479</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.955524016442688</v>
+        <v>1.709440417168033</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.955524279357819</v>
+        <v>1.709440680083164</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.955524196331988</v>
+        <v>1.709440597057333</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.955523988767411</v>
+        <v>1.709440389492756</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.95552400260505</v>
+        <v>1.709440403330394</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.955524140981434</v>
+        <v>1.709440541706779</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.955523857309846</v>
+        <v>1.70944025803519</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.955523684339365</v>
+        <v>1.70944008506471</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.955523580557077</v>
+        <v>1.709439981282421</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.95552372585228</v>
+        <v>1.709440126577625</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.955523968010954</v>
+        <v>1.709440368736298</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.955523795040473</v>
+        <v>1.709440195765818</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.955523497531246</v>
+        <v>1.709439898256591</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.955523483693607</v>
+        <v>1.709439884418952</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.955523116996188</v>
+        <v>1.709439517721532</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.955523116996188</v>
+        <v>1.709439517721532</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.955523054726815</v>
+        <v>1.709439455452159</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.955522950944526</v>
+        <v>1.709439351669871</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.955522777974045</v>
+        <v>1.70943917869939</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.95552282640578</v>
+        <v>1.709439227131125</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.95552246662718</v>
+        <v>1.709438867352525</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.955522425114265</v>
+        <v>1.709438825839609</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.955522480464818</v>
+        <v>1.709438881190163</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.955522535815372</v>
+        <v>1.709438936540717</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.955522577328288</v>
+        <v>1.709438978053633</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.955522307494338</v>
+        <v>1.709438708219682</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.955522362844891</v>
+        <v>1.709438763570236</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.955522508140096</v>
+        <v>1.70943890886544</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.955522473545999</v>
+        <v>1.709438874271344</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.955522459708361</v>
+        <v>1.709438860433706</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.955522549653011</v>
+        <v>1.709438950378356</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.955522867918695</v>
+        <v>1.70943926864404</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.955522688029395</v>
+        <v>1.70943908875474</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.955522729542311</v>
+        <v>1.709439130267655</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.955522542734192</v>
+        <v>1.709438943459537</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.955522611922384</v>
+        <v>1.709439012647728</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.955522411276626</v>
+        <v>1.709438812001971</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.955522452789542</v>
+        <v>1.709438853514887</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.462243845257878</v>
+        <v>-0.8369672081768307</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.955522480464818</v>
+        <v>1.709438881190163</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_2_000006.xlsx
+++ b/out/LSTM-S4_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002125145867466927</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.01999999999999985</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001470305025577545</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0008080378174781799</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0001270286738872528</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.1858502080323611</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0002199411392211914</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4652667921121084</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0006979536265134811</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0009049568325281143</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00141015462577343</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001762533560395241</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001678025349974632</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001419667154550552</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001376014202833176</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.316383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.00170324370265007</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.316383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001871736720204353</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.316383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002010917291045189</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002062777057290077</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002403344959020615</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002763615921139717</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.003129176795482635</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003087295219302177</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.116383792256578</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002786826342344284</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.116383792256578</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002520456910133362</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.116383792256578</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002491503953933716</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00271829217672348</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002652673050761223</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003081934526562691</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.116383792256578</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.003887876868247986</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.116383792256578</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003774974495172501</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.116383792256578</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003124676644802094</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.116383792256578</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.00266658328473568</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.116383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002219540998339653</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.00182715430855751</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001845890656113625</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002464940771460533</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002706646919250488</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002799063920974731</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.116383792256578</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002839095890522003</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.116383792256578</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002514446154236794</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.116383792256578</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002314858138561249</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002166524529457092</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002284636721014977</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002710634842514992</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003493253141641617</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.16</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002281487710230285</v>
+        <v>-8.163377695437521e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2936452402407034</v>
+        <v>0.1050690299055119</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.003467684611678123</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5878461985275054</v>
+        <v>0.2103369009567432</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06781475573950765</v>
+        <v>-0.02426475768171384</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.002122191712260246</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2256023357301727</v>
+        <v>0.08072263844684348</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001211874186992645</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2256023357301727</v>
+        <v>0.08072263844684348</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0009141899645328522</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2253644696726897</v>
+        <v>0.08070564184574713</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7307758094499195</v>
+        <v>0.05221723441119476</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.000484248623251915</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.688371559196363</v>
+        <v>0.1852440873864754</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1398257170095278</v>
+        <v>0.009991117342128746</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0007507354021072388</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.236180558841165</v>
+        <v>0.1529330111911204</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2449180041460473</v>
+        <v>0.01750038956321886</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0009190905839204788</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.58625970296179</v>
+        <v>0.1779478818911824</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1341262500444299</v>
+        <v>0.009582367974752299</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0009369589388370514</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.609382658935064</v>
+        <v>0.1795986677116514</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05539609458747302</v>
+        <v>0.003954778122239518</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.0005426481366157532</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.585907991945664</v>
+        <v>0.1779177354655771</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.06901878008344739</v>
+        <v>0.004928305666811993</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001082532107830048</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.668558755511534</v>
+        <v>0.1838206882788727</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04155763033690184</v>
+        <v>0.002965470960259378</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0005804169923067093</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.116383792256578</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.682609582166163</v>
+        <v>0.184820847879641</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03159586893928365</v>
+        <v>0.002253335709266774</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0004340708255767822</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4652667921121084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.704224749934308</v>
+        <v>0.1863616489902337</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01397441300868435</v>
+        <v>0.0009946647092385695</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.001302484422922134</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1858502080323611</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.700550362091587</v>
+        <v>0.1860942518832453</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01108768755469</v>
+        <v>0.0007869745093616778</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002580234780907631</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.708747297782685</v>
+        <v>0.1866757720554934</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005495755099007798</v>
+        <v>0.0003877324013388924</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001255771145224571</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.708644122956419</v>
+        <v>0.1866637420003894</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003192211619446865</v>
+        <v>0.0002248268589047337</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001020358875393867</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.709532796738187</v>
+        <v>0.1867229530833222</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001595060410096247</v>
+        <v>0.0001084588290795521</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003173299133777618</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.709525804554964</v>
+        <v>0.1867178118194207</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0007855282446549681</v>
+        <v>5.249296324763405e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.004924904555082321</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.709500793126515</v>
+        <v>0.1867113564428063</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004522584305726749</v>
+        <v>2.837652777902737e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006094338372349739</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.709622705614005</v>
+        <v>0.1867155862914633</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001490059378640617</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00751393660902977</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.709464744298975</v>
+        <v>0.1866995021382004</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.135689900721546e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.008375544100999832</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.709460603042515</v>
+        <v>0.186694565676186</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.658533421184461e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.009069865569472313</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.709462573524107</v>
+        <v>0.186690164547581</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.008591089397668839</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.70945617682695</v>
+        <v>0.1866850093590082</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.00795648992061615</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.709456019349447</v>
+        <v>0.1866855490269083</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.00768621452152729</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.709449352385576</v>
+        <v>0.1866852169235852</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007584258913993835</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.70944549031048</v>
+        <v>0.1866855974586429</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008291935548186302</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.709440942998295</v>
+        <v>0.1866858257796776</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009445689618587494</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.709441032942945</v>
+        <v>0.1866859157243276</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01049123425036669</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.70944017500936</v>
+        <v>0.1866850577907427</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0108231483027339</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.709440403330394</v>
+        <v>0.1866852861117774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01114569883793592</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.709439607666183</v>
+        <v>0.1866844904475657</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01159767806529999</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.709439669935556</v>
+        <v>0.1866845527169388</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01132888533174992</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.709439697610833</v>
+        <v>0.1866845803922156</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01055729296058416</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.709439849824856</v>
+        <v>0.1866847326062389</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01022155303508043</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.709439503883894</v>
+        <v>0.1866843866652772</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.009797714650630951</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.709439579990906</v>
+        <v>0.1866844627722888</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.00962858647108078</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.709439746042567</v>
+        <v>0.1866846288239504</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.008646810427308083</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.709440105821167</v>
+        <v>0.1866849886025505</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.007822183892130852</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.709440126577625</v>
+        <v>0.1866850093590082</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.007682466879487038</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.709440230359913</v>
+        <v>0.1866851131412967</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.008431641384959221</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.709440458680948</v>
+        <v>0.1866853414623313</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.009033100679516792</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.709440334142202</v>
+        <v>0.1866852169235852</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.009664151817560196</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.709440361817479</v>
+        <v>0.186685244598862</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.009550090879201889</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.709440417168033</v>
+        <v>0.186685299949416</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.009550269693136215</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.709440680083164</v>
+        <v>0.1866855628645467</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.009649300947785378</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.709440597057333</v>
+        <v>0.1866854798387159</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.009832050651311874</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.709440389492756</v>
+        <v>0.1866852722741391</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.00977744348347187</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.709440403330394</v>
+        <v>0.1866852861117774</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009603330865502357</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.709440541706779</v>
+        <v>0.1866854244881622</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.009845010936260223</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.70944025803519</v>
+        <v>0.1866851408165735</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01027095038443804</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.70944008506471</v>
+        <v>0.1866849678460928</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.009942522272467613</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.709439981282421</v>
+        <v>0.1866848640638043</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.009717851877212524</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.709440126577625</v>
+        <v>0.1866850093590082</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.009584464132785797</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.709440368736298</v>
+        <v>0.1866852515176814</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.009537918493151665</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.709440195765818</v>
+        <v>0.1866850785472004</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.009681649506092072</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.709439898256591</v>
+        <v>0.1866847810379735</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.009866887703537941</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.709439884418952</v>
+        <v>0.1866847672003349</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01009074971079826</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.709439517721532</v>
+        <v>0.1866844005029157</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.009926959872245789</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.709439517721532</v>
+        <v>0.1866844005029157</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.009646207094192505</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.709439455452159</v>
+        <v>0.1866843382335426</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.009748434647917747</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.709439351669871</v>
+        <v>0.1866842344512541</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.009718563407659531</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.70943917869939</v>
+        <v>0.1866840614807734</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.009440895169973373</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.709439227131125</v>
+        <v>0.1866841099125079</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.009055301547050476</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.709438867352525</v>
+        <v>0.1866837501339079</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.00870731845498085</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.709438825839609</v>
+        <v>0.1866837086209925</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.007926275953650475</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.709438881190163</v>
+        <v>0.1866837639715462</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.007345354184508324</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.709438936540717</v>
+        <v>0.1866838193221002</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.006697291508316994</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.709438978053633</v>
+        <v>0.1866838608350155</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006162362173199654</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.709438708219682</v>
+        <v>0.1866835910010654</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.005518518388271332</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.709438763570236</v>
+        <v>0.1866836463516194</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005059897899627686</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.70943890886544</v>
+        <v>0.1866837916468233</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004861626774072647</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.709438874271344</v>
+        <v>0.1866837570527271</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.004759505391120911</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.709438860433706</v>
+        <v>0.1866837432150885</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004271045327186584</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.709438950378356</v>
+        <v>0.1866838331597387</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003434153273701668</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.70943926864404</v>
+        <v>0.1866841514254233</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004054239019751549</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.70943908875474</v>
+        <v>0.1866839715361232</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004860149696469307</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8369672081768307</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.709439130267655</v>
+        <v>0.1866840130490386</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.00518166646361351</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.709438943459537</v>
+        <v>0.1866838262409193</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005385270342230797</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.709439012647728</v>
+        <v>0.1866838954291118</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.005423316732048988</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.709438812001971</v>
+        <v>0.1866836947833539</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005379550158977509</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.3</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.709438853514887</v>
+        <v>0.1866837362962693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.005058979615569115</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8369672081768307</v>
+        <v>-0.3</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.709438881190163</v>
+        <v>0.1866837639715462</v>
       </c>
     </row>
   </sheetData>
